--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入出金・売上" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="入出金・売上" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1336,42 +1336,327 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>―（未記載）</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>振込入金 1件 ※金額未記載・Web21で要確認</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>通知2026-09-10 00:11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-10 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15350</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>連絡番号0910070553(001)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-10 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>―（未記載）</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>出金/振込 複数件（振込メモ：7月(末)〆マージン支払い・小口現金）※金額未記載・Web21で要確認</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Web21振込受付5件・出金通知4件</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-10 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9740</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Square（カード決済）</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>売上：総売上¥8,855＋税¥885＝税込¥9,740・手数料¥351・純受取¥9,389（9/18京信着金＝重複計上せず）</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>日次サマリー2026/9/12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-12 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>70220</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>出金 4件</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>連絡番号0914083785(001)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-14 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>―（未記載）</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>振込入金 1件 ※金額未記載・Web21で要確認</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>通知2026-09-16 23:51</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-16 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>―（未記載）</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>振込入金 1件 ※金額未記載・Web21で要確認</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>通知番号20260918-10127205</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-09-17 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>（着金9,389）</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>入金 1件《着金》Square純受取¥9,389の着金（9/12売上¥9,740の実入金＝重複計上せず）</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>連絡番号0918106650(001)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-09-18 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>508140</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の入金2件は金額未記載のため未算入。Square売上¥9,400で計上済み。8/28京信着金¥9,062は同売上の実入金のため重複算入せず</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="C34" t="n">
+        <v>533230</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>※三井住友の入金5件は金額未記載のため未算入。Square売上は税込¥9,740で計上（9/18京信着金¥9,389は同売上の実入金のため重複算入せず）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>618791</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>※三井住友の出金3件は金額未記載のため未算入</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>※三井住友の出金3件は金額未記載のため未算入。9/7京信 出金30,110円を追加</t>
+      <c r="C35" t="n">
+        <v>689011</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>※三井住友の出金（未記載）は未算入。9/14京信 出金70,220円（4件）を追加</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1628,35 +1628,282 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Square（カード決済）</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>売上：総売上¥10,000＋税¥1,000＝税込¥11,000・手数料¥396・純受取¥10,604（9/25 京信着金＝重複計上せず）</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>日次売上サマリー</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-09-20 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>350</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>連絡番号0924113374(001)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-09-24 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>連絡番号0924113374(001)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-09-24 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5450</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>連絡番号0924119462(001)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-09-24 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>連絡番号0924119462(001)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-09-24 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>（着金10,604）</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>入金 1件《着金》Square純受取¥10,604の着金（9/20売上¥11,000の実入金＝重複計上せず）</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>連絡番号0925132024(001)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-25 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>連絡番号0925132599(001)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-09-25 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>533230</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>※三井住友の入金5件は金額未記載のため未算入。Square売上は税込¥9,740で計上（9/18京信着金¥9,389は同売上の実入金のため重複算入せず）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="C41" t="n">
+        <v>550030</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>※三井住友の入金は金額未記載のため未算入。Square売上は税込計上（9/18¥9,389・9/25¥10,604の京信着金は同売上の実入金のため重複算入せず）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>689011</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>※三井住友の出金（未記載）は未算入。9/14京信 出金70,220円（4件）を追加</t>
+      <c r="C42" t="n">
+        <v>729011</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>※三井住友の出金（未記載）は未算入。9/24京信 出金20,000＋10,000、9/25 出金10,000を追加</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1875,35 +1875,105 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>28000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>入金 1件</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>連絡番号0928139514(001)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-09-28 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>出金 1件</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>連絡番号0928143474(001)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-09-28 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>550030</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>※三井住友の入金は金額未記載のため未算入。Square売上は税込計上（9/18¥9,389・9/25¥10,604の京信着金は同売上の実入金のため重複算入せず）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
+      <c r="C43" t="n">
+        <v>578030</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>※三井住友の入金は金額未記載のため未算入。Square売上は税込計上（京信着金は同売上の実入金のため重複算入せず）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>729011</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>※三井住友の出金（未記載）は未算入。9/24京信 出金20,000＋10,000、9/25 出金10,000を追加</t>
+      <c r="C44" t="n">
+        <v>749011</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>※三井住友の出金（未記載）は未算入。9/28京信 入金28,000・出金20,000を追加</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1945,35 +1945,72 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>―（未記載）</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>三井住友銀行（トランクNORTH支店 普通）</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>出金 1件 ※金額メール未記載・Web21「入出金明細照会」で要確認</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>通知番号20260930-10088283</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-09-29 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C44" t="n">
         <v>578030</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>※三井住友の入金は金額未記載のため未算入。Square売上は税込計上（京信着金は同売上の実入金のため重複算入せず）</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
+    <row r="45">
+      <c r="B45" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C45" t="n">
         <v>749011</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>※三井住友の出金（未記載）は未算入。9/28京信 入金28,000・出金20,000を追加</t>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>※三井住友の出金（未記載）は未算入。9/29 三井住友 出金1件（金額未記載）を追加</t>
         </is>
       </c>
     </row>

--- a/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
+++ b/company/secretary/経理/売上帳簿/入出金・売上帳簿_2026.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1982,35 +1982,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>京都信用金庫（北野支店 普通）</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>出金 1件（BB手数料の可能性）</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>連絡番号1001171116(001)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-01 転送受信</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>（集計）</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C45" t="n">
         <v>578030</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>※三井住友の入金は金額未記載のため未算入。Square売上は税込計上（京信着金は同売上の実入金のため重複算入せず）</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
+    <row r="46">
+      <c r="B46" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>749011</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>※三井住友の出金（未記載）は未算入。9/29 三井住友 出金1件（金額未記載）を追加</t>
+      <c r="C46" t="n">
+        <v>750111</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>※三井住友の出金（未記載）は未算入。10/1 京信 出金1,100円（BB手数料）を追加</t>
         </is>
       </c>
     </row>
